--- a/source/AU/TD_AUv3_Restructure(1).xlsx
+++ b/source/AU/TD_AUv3_Restructure(1).xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2590" uniqueCount="787">
   <si>
     <t xml:space="preserve">APPN Adelaide University vocabularies</t>
   </si>
@@ -2792,9 +2792,6 @@
   </si>
   <si>
     <t xml:space="preserve">Reach-in growth chamber (Conviron, PGC 20) with temperature range of temperature lights on 10 to 40 lights off 4 to 40. Size 1.9 m2, height 1.46 m, lights light 20 - 1000. Non-PC2 containment level and gas supply, co2 to 3000 ppm. With humidity up to 90%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">non-PC2</t>
   </si>
   <si>
     <t xml:space="preserve">RI.5</t>
@@ -3242,6 +3239,7 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="4"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -7685,15 +7683,13 @@
       <c r="P42" s="275" t="n">
         <v>100169</v>
       </c>
-      <c r="Q42" s="275" t="s">
-        <v>714</v>
-      </c>
+      <c r="Q42" s="275"/>
       <c r="R42" s="275"/>
       <c r="S42" s="296"/>
     </row>
     <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="275" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B43" s="304" t="s">
         <v>713</v>
@@ -7730,18 +7726,16 @@
       <c r="P43" s="275" t="n">
         <v>100170</v>
       </c>
-      <c r="Q43" s="275" t="s">
-        <v>714</v>
-      </c>
+      <c r="Q43" s="275"/>
       <c r="R43" s="275"/>
       <c r="S43" s="296"/>
     </row>
     <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="297" t="s">
+        <v>715</v>
+      </c>
+      <c r="B44" s="266" t="s">
         <v>716</v>
-      </c>
-      <c r="B44" s="266" t="s">
-        <v>717</v>
       </c>
       <c r="C44" s="301" t="s">
         <v>702</v>
@@ -7770,23 +7764,21 @@
         <v>708</v>
       </c>
       <c r="O44" s="275" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P44" s="275" t="n">
         <v>100165</v>
       </c>
-      <c r="Q44" s="275" t="s">
-        <v>714</v>
-      </c>
+      <c r="Q44" s="275"/>
       <c r="R44" s="275"/>
       <c r="S44" s="296"/>
     </row>
     <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="275" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B45" s="304" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C45" s="302" t="s">
         <v>702</v>
@@ -7815,37 +7807,35 @@
         <v>708</v>
       </c>
       <c r="O45" s="275" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P45" s="275" t="n">
         <v>100164</v>
       </c>
-      <c r="Q45" s="275" t="s">
-        <v>714</v>
-      </c>
+      <c r="Q45" s="275"/>
       <c r="R45" s="275"/>
       <c r="S45" s="296"/>
     </row>
     <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="297" t="s">
+        <v>719</v>
+      </c>
+      <c r="B46" s="266" t="s">
         <v>720</v>
       </c>
-      <c r="B46" s="266" t="s">
+      <c r="C46" s="305" t="s">
         <v>721</v>
-      </c>
-      <c r="C46" s="305" t="s">
-        <v>722</v>
       </c>
       <c r="D46" s="295"/>
       <c r="E46" s="248" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F46" s="248" t="s">
         <v>704</v>
       </c>
       <c r="G46" s="295"/>
       <c r="H46" s="248" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="I46" s="248"/>
       <c r="J46" s="248" t="s">
@@ -7858,10 +7848,10 @@
         <v>708</v>
       </c>
       <c r="O46" s="275" t="s">
+        <v>724</v>
+      </c>
+      <c r="P46" s="275" t="s">
         <v>725</v>
-      </c>
-      <c r="P46" s="275" t="s">
-        <v>726</v>
       </c>
       <c r="Q46" s="275" t="s">
         <v>610</v>
@@ -7871,27 +7861,27 @@
     </row>
     <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="306" t="s">
+        <v>726</v>
+      </c>
+      <c r="B47" s="307" t="s">
         <v>727</v>
       </c>
-      <c r="B47" s="307" t="s">
-        <v>728</v>
-      </c>
       <c r="C47" s="297" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D47" s="295"/>
       <c r="E47" s="248" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F47" s="248" t="s">
         <v>704</v>
       </c>
       <c r="G47" s="295"/>
       <c r="H47" s="248" t="s">
+        <v>728</v>
+      </c>
+      <c r="I47" s="248" t="s">
         <v>729</v>
-      </c>
-      <c r="I47" s="248" t="s">
-        <v>730</v>
       </c>
       <c r="J47" s="248" t="s">
         <v>707</v>
@@ -7903,10 +7893,10 @@
         <v>708</v>
       </c>
       <c r="O47" s="275" t="s">
+        <v>730</v>
+      </c>
+      <c r="P47" s="275" t="s">
         <v>731</v>
-      </c>
-      <c r="P47" s="275" t="s">
-        <v>732</v>
       </c>
       <c r="Q47" s="275" t="s">
         <v>610</v>
@@ -7916,24 +7906,24 @@
     </row>
     <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="275" t="s">
+        <v>732</v>
+      </c>
+      <c r="B48" s="304" t="s">
         <v>733</v>
       </c>
-      <c r="B48" s="304" t="s">
-        <v>734</v>
-      </c>
       <c r="C48" s="305" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D48" s="295"/>
       <c r="E48" s="248" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F48" s="248" t="s">
         <v>704</v>
       </c>
       <c r="G48" s="295"/>
       <c r="H48" s="248" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I48" s="248"/>
       <c r="J48" s="248" t="s">
@@ -7946,7 +7936,7 @@
         <v>708</v>
       </c>
       <c r="O48" s="275" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="P48" s="275" t="n">
         <v>100162</v>
@@ -7959,24 +7949,24 @@
     </row>
     <row r="49" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="297" t="s">
+        <v>737</v>
+      </c>
+      <c r="B49" s="258" t="s">
         <v>738</v>
       </c>
-      <c r="B49" s="258" t="s">
-        <v>739</v>
-      </c>
       <c r="C49" s="297" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D49" s="295"/>
       <c r="E49" s="248" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F49" s="248" t="s">
         <v>704</v>
       </c>
       <c r="G49" s="295"/>
       <c r="H49" s="248" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="I49" s="248" t="s">
         <v>706</v>
@@ -7991,7 +7981,7 @@
         <v>708</v>
       </c>
       <c r="O49" s="275" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="P49" s="275" t="n">
         <v>100163</v>
@@ -8004,24 +7994,24 @@
     </row>
     <row r="50" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="303" t="s">
+        <v>739</v>
+      </c>
+      <c r="B50" s="266" t="s">
         <v>740</v>
       </c>
-      <c r="B50" s="266" t="s">
-        <v>741</v>
-      </c>
       <c r="C50" s="303" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D50" s="295"/>
       <c r="E50" s="248" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F50" s="248" t="s">
         <v>704</v>
       </c>
       <c r="G50" s="295"/>
       <c r="H50" s="248" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I50" s="248"/>
       <c r="J50" s="248" t="s">
@@ -8034,37 +8024,35 @@
         <v>708</v>
       </c>
       <c r="O50" s="275" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="P50" s="275" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q50" s="275" t="s">
-        <v>714</v>
-      </c>
+        <v>741</v>
+      </c>
+      <c r="Q50" s="275"/>
       <c r="R50" s="275"/>
       <c r="S50" s="296"/>
     </row>
     <row r="51" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="303" t="s">
+        <v>742</v>
+      </c>
+      <c r="B51" s="271" t="s">
         <v>743</v>
       </c>
-      <c r="B51" s="271" t="s">
-        <v>744</v>
-      </c>
       <c r="C51" s="305" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D51" s="295"/>
       <c r="E51" s="248" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F51" s="248" t="s">
         <v>704</v>
       </c>
       <c r="G51" s="295"/>
       <c r="H51" s="248" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I51" s="248" t="s">
         <v>706</v>
@@ -8079,40 +8067,38 @@
         <v>708</v>
       </c>
       <c r="O51" s="275" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="P51" s="275" t="s">
-        <v>745</v>
-      </c>
-      <c r="Q51" s="275" t="s">
-        <v>714</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="Q51" s="275"/>
       <c r="R51" s="275"/>
       <c r="S51" s="296"/>
     </row>
     <row r="52" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="303" t="s">
+        <v>745</v>
+      </c>
+      <c r="B52" s="271" t="s">
         <v>746</v>
       </c>
-      <c r="B52" s="271" t="s">
-        <v>747</v>
-      </c>
       <c r="C52" s="297" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D52" s="295"/>
       <c r="E52" s="248" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F52" s="248" t="s">
         <v>704</v>
       </c>
       <c r="G52" s="295"/>
       <c r="H52" s="248" t="s">
+        <v>747</v>
+      </c>
+      <c r="I52" s="248" t="s">
         <v>748</v>
-      </c>
-      <c r="I52" s="248" t="s">
-        <v>749</v>
       </c>
       <c r="J52" s="248" t="s">
         <v>707</v>
@@ -8124,7 +8110,7 @@
         <v>708</v>
       </c>
       <c r="O52" s="275" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="P52" s="275" t="n">
         <v>170166</v>
@@ -8137,27 +8123,27 @@
     </row>
     <row r="53" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="306" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B53" s="304" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C53" s="303" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D53" s="295"/>
       <c r="E53" s="248" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F53" s="248" t="s">
         <v>704</v>
       </c>
       <c r="G53" s="295"/>
       <c r="H53" s="248" t="s">
+        <v>747</v>
+      </c>
+      <c r="I53" s="248" t="s">
         <v>748</v>
-      </c>
-      <c r="I53" s="248" t="s">
-        <v>749</v>
       </c>
       <c r="J53" s="248" t="s">
         <v>707</v>
@@ -8169,7 +8155,7 @@
         <v>708</v>
       </c>
       <c r="O53" s="275" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="P53" s="275" t="n">
         <v>170165</v>
@@ -8182,29 +8168,29 @@
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="303" t="s">
+        <v>751</v>
+      </c>
+      <c r="B54" s="266" t="s">
         <v>752</v>
-      </c>
-      <c r="B54" s="266" t="s">
-        <v>753</v>
       </c>
       <c r="C54" s="303" t="s">
         <v>702</v>
       </c>
       <c r="D54" s="295"/>
       <c r="E54" s="248" t="s">
+        <v>753</v>
+      </c>
+      <c r="F54" s="248" t="s">
         <v>754</v>
       </c>
-      <c r="F54" s="248" t="s">
+      <c r="G54" s="248" t="s">
         <v>755</v>
       </c>
-      <c r="G54" s="248" t="s">
+      <c r="H54" s="248" t="s">
         <v>756</v>
       </c>
-      <c r="H54" s="248" t="s">
+      <c r="I54" s="248" t="s">
         <v>757</v>
-      </c>
-      <c r="I54" s="248" t="s">
-        <v>758</v>
       </c>
       <c r="J54" s="248"/>
       <c r="K54" s="295"/>
@@ -8225,39 +8211,39 @@
     </row>
     <row r="55" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="305" t="s">
+        <v>758</v>
+      </c>
+      <c r="B55" s="271" t="s">
         <v>759</v>
-      </c>
-      <c r="B55" s="271" t="s">
-        <v>760</v>
       </c>
       <c r="C55" s="299" t="s">
         <v>702</v>
       </c>
       <c r="D55" s="295"/>
       <c r="E55" s="248" t="s">
+        <v>760</v>
+      </c>
+      <c r="F55" s="248" t="s">
         <v>761</v>
       </c>
-      <c r="F55" s="248" t="s">
+      <c r="G55" s="248" t="s">
         <v>762</v>
       </c>
-      <c r="G55" s="248" t="s">
+      <c r="H55" s="248" t="s">
         <v>763</v>
       </c>
-      <c r="H55" s="248" t="s">
+      <c r="I55" s="248" t="s">
         <v>764</v>
-      </c>
-      <c r="I55" s="248" t="s">
-        <v>765</v>
       </c>
       <c r="J55" s="248"/>
       <c r="K55" s="295"/>
       <c r="L55" s="295"/>
       <c r="M55" s="295"/>
       <c r="N55" s="253" t="s">
+        <v>765</v>
+      </c>
+      <c r="O55" s="275" t="s">
         <v>766</v>
-      </c>
-      <c r="O55" s="275" t="s">
-        <v>767</v>
       </c>
       <c r="P55" s="275"/>
       <c r="Q55" s="275" t="s">
@@ -8373,17 +8359,17 @@
     </row>
     <row r="2" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="309" t="s">
+        <v>767</v>
+      </c>
+      <c r="B2" s="309" t="s">
         <v>768</v>
       </c>
-      <c r="B2" s="309" t="s">
+      <c r="C2" s="310" t="s">
         <v>769</v>
-      </c>
-      <c r="C2" s="310" t="s">
-        <v>770</v>
       </c>
       <c r="D2" s="310"/>
       <c r="E2" s="311" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8391,77 +8377,77 @@
         <v>702</v>
       </c>
       <c r="B3" s="309" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C3" s="309"/>
       <c r="D3" s="309"/>
       <c r="E3" s="311" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="309" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B4" s="309" t="s">
+        <v>773</v>
+      </c>
+      <c r="C4" s="310" t="s">
         <v>774</v>
       </c>
-      <c r="C4" s="310" t="s">
+      <c r="D4" s="310" t="s">
         <v>775</v>
       </c>
-      <c r="D4" s="310" t="s">
+      <c r="E4" s="311" t="s">
         <v>776</v>
-      </c>
-      <c r="E4" s="311" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="66.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="312" t="s">
+        <v>777</v>
+      </c>
+      <c r="B5" s="312" t="s">
         <v>778</v>
       </c>
-      <c r="B5" s="312" t="s">
+      <c r="C5" s="313" t="s">
         <v>779</v>
-      </c>
-      <c r="C5" s="313" t="s">
-        <v>780</v>
       </c>
       <c r="D5" s="312"/>
       <c r="E5" s="311" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="312" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B6" s="312"/>
       <c r="C6" s="312"/>
       <c r="D6" s="312"/>
       <c r="E6" s="311" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="312" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B7" s="312"/>
       <c r="C7" s="312"/>
       <c r="D7" s="312"/>
       <c r="E7" s="312" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="312" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B8" s="312"/>
       <c r="C8" s="312"/>
       <c r="D8" s="312"/>
       <c r="E8" s="311" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
   </sheetData>
